--- a/data/reporting_months.xlsx
+++ b/data/reporting_months.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,6 +1835,282 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
